--- a/posicoes/BTG.xlsx
+++ b/posicoes/BTG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R88acb1fab6b84c03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Rdd5f64014edd461f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -267,7 +267,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14063154</x:v>
+        <x:v>10492152</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -355,7 +355,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15594421</x:v>
+        <x:v>16725230</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -423,7 +423,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10285562</x:v>
+        <x:v>11701685</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -501,7 +501,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18479496</x:v>
+        <x:v>7108262</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +579,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15177448</x:v>
+        <x:v>6351014</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -623,16 +623,16 @@
         <x:v>7460.37193970563</x:v>
       </x:c>
       <x:c>
-        <x:v>11116.14</x:v>
-      </x:c>
-      <x:c>
-        <x:v>140.37</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>10975.77</x:v>
+        <x:v>11122.59</x:v>
+      </x:c>
+      <x:c>
+        <x:v>141.66</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>10980.93</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -659,7 +659,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10262257</x:v>
+        <x:v>11776870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -703,16 +703,16 @@
         <x:v>4675.79311541</x:v>
       </x:c>
       <x:c>
-        <x:v>22274.46</x:v>
-      </x:c>
-      <x:c>
-        <x:v>941.17</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>21333.29</x:v>
+        <x:v>22288.06</x:v>
+      </x:c>
+      <x:c>
+        <x:v>943.21</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>21344.85</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -739,7 +739,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11487841</x:v>
+        <x:v>13341560</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -783,16 +783,16 @@
         <x:v>3000</x:v>
       </x:c>
       <x:c>
-        <x:v>32270.92</x:v>
-      </x:c>
-      <x:c>
-        <x:v>358.18</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>31912.74</x:v>
+        <x:v>32276.67</x:v>
+      </x:c>
+      <x:c>
+        <x:v>359.33</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>31917.34</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -819,7 +819,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9729161</x:v>
+        <x:v>11182819</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -899,7 +899,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2403698</x:v>
+        <x:v>3315735</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -979,7 +979,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4072718</x:v>
+        <x:v>715753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +1059,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>867384</x:v>
+        <x:v>2046954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1103,16 +1103,16 @@
         <x:v>196.80454512</x:v>
       </x:c>
       <x:c>
-        <x:v>209039.48</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1469.49</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>207569.99</x:v>
+        <x:v>209105.23</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1479.35</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>207625.88</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -1139,7 +1139,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18397255</x:v>
+        <x:v>15378324</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1183,16 +1183,16 @@
         <x:v>149.43216</x:v>
       </x:c>
       <x:c>
-        <x:v>172187.7</x:v>
-      </x:c>
-      <x:c>
-        <x:v>3413.33</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>168774.37</x:v>
+        <x:v>172305.24</x:v>
+      </x:c>
+      <x:c>
+        <x:v>3430.96</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>168874.28</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -1219,7 +1219,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18307654</x:v>
+        <x:v>14852251</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1311,7 +1311,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3600049</x:v>
+        <x:v>332698</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1403,7 +1403,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3634180</x:v>
+        <x:v>631904</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1495,7 +1495,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3648770</x:v>
+        <x:v>619032</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1587,7 +1587,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17462495</x:v>
+        <x:v>14435141</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1679,7 +1679,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5632235</x:v>
+        <x:v>6284512</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1771,7 +1771,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16762614</x:v>
+        <x:v>13862802</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1863,7 +1863,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11271137</x:v>
+        <x:v>13001689</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1955,7 +1955,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>614454</x:v>
+        <x:v>1430809</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2047,7 +2047,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10734769</x:v>
+        <x:v>12083674</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2139,7 +2139,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12079103</x:v>
+        <x:v>8337530</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2231,7 +2231,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15343597</x:v>
+        <x:v>16513108</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2323,7 +2323,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12829959</x:v>
+        <x:v>8833057</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2415,7 +2415,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9738761</x:v>
+        <x:v>10866256</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2507,7 +2507,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19076854</x:v>
+        <x:v>15753226</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2551,14 +2551,14 @@
         <x:v>5</x:v>
       </x:c>
       <x:c>
-        <x:v>70.2</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>70.2</x:v>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>70</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -2585,7 +2585,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8902007</x:v>
+        <x:v>3030230</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2629,14 +2629,14 @@
         <x:v>76</x:v>
       </x:c>
       <x:c>
-        <x:v>3283.2</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>3283.2</x:v>
+        <x:v>3262.68</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>3262.68</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -2663,7 +2663,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9064638</x:v>
+        <x:v>10404219</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2733,7 +2733,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13738213</x:v>
+        <x:v>10279271</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2803,7 +2803,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16264173</x:v>
+        <x:v>17987562</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2871,7 +2871,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31661111</x:v>
+        <x:v>33807799</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2915,16 +2915,16 @@
         <x:v>229.0788549</x:v>
       </x:c>
       <x:c>
-        <x:v>75081.01</x:v>
-      </x:c>
-      <x:c>
-        <x:v>633.57</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>74447.44</x:v>
+        <x:v>75113.95</x:v>
+      </x:c>
+      <x:c>
+        <x:v>640.68</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>74473.27</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -2951,7 +2951,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8958414</x:v>
+        <x:v>20170368</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3031,7 +3031,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26706064</x:v>
+        <x:v>28849439</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3111,7 +3111,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30063817</x:v>
+        <x:v>32320656</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3191,7 +3191,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31061217</x:v>
+        <x:v>33459763</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3271,7 +3271,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19901826</x:v>
+        <x:v>9134800</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3351,7 +3351,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28804698</x:v>
+        <x:v>26733805</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3431,7 +3431,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20810882</x:v>
+        <x:v>12438718</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3475,16 +3475,16 @@
         <x:v>29040.5557123</x:v>
       </x:c>
       <x:c>
-        <x:v>30824.16</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>30824.16</x:v>
+        <x:v>30810.33</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>30810.33</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -3511,7 +3511,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25623895</x:v>
+        <x:v>27795451</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3603,7 +3603,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26567166</x:v>
+        <x:v>28941365</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3695,7 +3695,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22941119</x:v>
+        <x:v>25199295</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3787,7 +3787,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20384860</x:v>
+        <x:v>9186434</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3879,7 +3879,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21501185</x:v>
+        <x:v>23984823</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3971,7 +3971,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10241869</x:v>
+        <x:v>20503042</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4063,7 +4063,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32807246</x:v>
+        <x:v>30707382</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4155,7 +4155,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27351802</x:v>
+        <x:v>29750584</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4247,7 +4247,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27602720</x:v>
+        <x:v>25811798</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4339,7 +4339,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32429586</x:v>
+        <x:v>30492471</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4431,7 +4431,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22067869</x:v>
+        <x:v>24432236</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4523,7 +4523,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25996497</x:v>
+        <x:v>28522365</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4615,7 +4615,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29559322</x:v>
+        <x:v>27615881</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4707,7 +4707,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19565333</x:v>
+        <x:v>1605465</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4799,7 +4799,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33824553</x:v>
+        <x:v>31837123</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4891,7 +4891,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29106966</x:v>
+        <x:v>26988673</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4983,7 +4983,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22872214</x:v>
+        <x:v>25264111</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5075,7 +5075,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23915585</x:v>
+        <x:v>22003648</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5167,7 +5167,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25481848</x:v>
+        <x:v>28018664</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5259,7 +5259,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27230567</x:v>
+        <x:v>29392418</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5351,7 +5351,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10622576</x:v>
+        <x:v>20310772</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5395,14 +5395,14 @@
         <x:v>460</x:v>
       </x:c>
       <x:c>
-        <x:v>42734</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>42734</x:v>
+        <x:v>42559.2</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>42559.2</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -5429,7 +5429,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24646993</x:v>
+        <x:v>13516868</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5473,14 +5473,14 @@
         <x:v>1155</x:v>
       </x:c>
       <x:c>
-        <x:v>110302.5</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>110302.5</x:v>
+        <x:v>109159.05</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>109159.05</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -5507,7 +5507,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22121022</x:v>
+        <x:v>33536984</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5551,14 +5551,14 @@
         <x:v>694</x:v>
       </x:c>
       <x:c>
-        <x:v>63841.06</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>63841.06</x:v>
+        <x:v>64014.56</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>64014.56</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -5585,7 +5585,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24511146</x:v>
+        <x:v>27700990</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5629,14 +5629,14 @@
         <x:v>565</x:v>
       </x:c>
       <x:c>
-        <x:v>56488.7</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>56488.7</x:v>
+        <x:v>56313.55</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>56313.55</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -5663,7 +5663,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23200579</x:v>
+        <x:v>27837897</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5733,7 +5733,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26315357</x:v>
+        <x:v>28727336</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5803,7 +5803,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26209140</x:v>
+        <x:v>28347677</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5891,7 +5891,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23030331</x:v>
+        <x:v>25153191</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5959,7 +5959,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33551876</x:v>
+        <x:v>31476807</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6039,7 +6039,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29814590</x:v>
+        <x:v>32069223</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6119,7 +6119,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21389289</x:v>
+        <x:v>23545630</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6203,7 +6203,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>30737856</x:v>
+        <x:v>33253153</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6287,7 +6287,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>29306677</x:v>
+        <x:v>27327600</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6371,7 +6371,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>30047330</x:v>
+        <x:v>32335795</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6455,7 +6455,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>26422252</x:v>
+        <x:v>28582772</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6547,7 +6547,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28087673</x:v>
+        <x:v>26427350</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6639,7 +6639,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32385581</x:v>
+        <x:v>30547153</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6731,7 +6731,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25725365</x:v>
+        <x:v>28302018</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6823,7 +6823,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33796973</x:v>
+        <x:v>31842788</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6915,7 +6915,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>36583</x:v>
+        <x:v>17363499</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6993,7 +6993,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26734499</x:v>
+        <x:v>28845215</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7071,7 +7071,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21939331</x:v>
+        <x:v>24015826</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7149,7 +7149,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29558111</x:v>
+        <x:v>27614840</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7227,7 +7227,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17595081</x:v>
+        <x:v>21103437</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7305,7 +7305,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21125751</x:v>
+        <x:v>12681813</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7383,7 +7383,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29703501</x:v>
+        <x:v>32225077</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7461,7 +7461,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21454505</x:v>
+        <x:v>23478332</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7539,7 +7539,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25203024</x:v>
+        <x:v>23408260</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7617,7 +7617,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27257342</x:v>
+        <x:v>29824452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7695,7 +7695,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28374407</x:v>
+        <x:v>26673692</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7773,7 +7773,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5573363</x:v>
+        <x:v>19800865</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7851,7 +7851,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21997354</x:v>
+        <x:v>24037076</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7929,7 +7929,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25513597</x:v>
+        <x:v>27917678</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8007,7 +8007,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1307394</x:v>
+        <x:v>19618673</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8085,7 +8085,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23977171</x:v>
+        <x:v>21967639</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8163,7 +8163,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32001459</x:v>
+        <x:v>29927362</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8241,7 +8241,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30091235</x:v>
+        <x:v>32378482</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8319,7 +8319,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24171818</x:v>
+        <x:v>22276536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8389,7 +8389,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30077697</x:v>
+        <x:v>32334501</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8459,7 +8459,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9274030</x:v>
+        <x:v>19975827</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8529,7 +8529,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24970342</x:v>
+        <x:v>23030902</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8599,7 +8599,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25503752</x:v>
+        <x:v>27908609</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8669,7 +8669,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20814698</x:v>
+        <x:v>12461259</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8739,7 +8739,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24200648</x:v>
+        <x:v>22305168</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8809,7 +8809,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16828190</x:v>
+        <x:v>21235872</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8879,7 +8879,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23609389</x:v>
+        <x:v>21866165</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8949,7 +8949,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21859760</x:v>
+        <x:v>24173336</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9019,7 +9019,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32687236</x:v>
+        <x:v>30844791</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9087,7 +9087,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25089017</x:v>
+        <x:v>22733410</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9131,16 +9131,16 @@
         <x:v>32917.6765595</x:v>
       </x:c>
       <x:c>
-        <x:v>55551.23</x:v>
-      </x:c>
-      <x:c>
-        <x:v>665.6</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>54885.63</x:v>
+        <x:v>55576.34</x:v>
+      </x:c>
+      <x:c>
+        <x:v>669.99</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>54906.35</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -9167,7 +9167,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16780073</x:v>
+        <x:v>20896797</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9211,16 +9211,16 @@
         <x:v>10784.950882</x:v>
       </x:c>
       <x:c>
-        <x:v>21103.97</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>21103.97</x:v>
+        <x:v>21034.59</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>21034.59</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -9247,7 +9247,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25479074</x:v>
+        <x:v>27520812</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9327,7 +9327,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20062276</x:v>
+        <x:v>3895056</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9371,16 +9371,16 @@
         <x:v>10935.210624</x:v>
       </x:c>
       <x:c>
-        <x:v>23630.96</x:v>
-      </x:c>
-      <x:c>
-        <x:v>331.58</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>23299.38</x:v>
+        <x:v>23517.62</x:v>
+      </x:c>
+      <x:c>
+        <x:v>311.74</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>23205.88</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -9407,7 +9407,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20518206</x:v>
+        <x:v>9337719</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9487,7 +9487,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9241833</x:v>
+        <x:v>20256573</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9567,7 +9567,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28730611</x:v>
+        <x:v>26376398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9611,16 +9611,16 @@
         <x:v>33773.50649</x:v>
       </x:c>
       <x:c>
-        <x:v>75312.22</x:v>
-      </x:c>
-      <x:c>
-        <x:v>872.65</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>74439.57</x:v>
+        <x:v>75354.53</x:v>
+      </x:c>
+      <x:c>
+        <x:v>880.05</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>74474.48</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -9647,7 +9647,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29832406</x:v>
+        <x:v>31589905</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9727,7 +9727,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5463515</x:v>
+        <x:v>19668673</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9807,7 +9807,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10699416</x:v>
+        <x:v>20542915</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9851,16 +9851,16 @@
         <x:v>139.8694019</x:v>
       </x:c>
       <x:c>
-        <x:v>3305.27</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>3305.27</x:v>
+        <x:v>3290.86</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>3290.86</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -9887,7 +9887,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32953266</x:v>
+        <x:v>30629450</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9967,7 +9967,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25964632</x:v>
+        <x:v>28090241</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10015,12 +10015,12 @@
         <x:v>11367.483461</x:v>
       </x:c>
       <x:c>
-        <x:v>18619.16</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c>
-        <x:v>18619.16</x:v>
+        <x:v>18627.23</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c>
+        <x:v>18627.23</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -10051,7 +10051,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>27527997</x:v>
+        <x:v>21278401</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10099,12 +10099,12 @@
         <x:v>102113.41644278</x:v>
       </x:c>
       <x:c>
-        <x:v>167254.82</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c>
-        <x:v>167254.82</x:v>
+        <x:v>167327.31</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c>
+        <x:v>167327.31</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -10135,7 +10135,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>21149180</x:v>
+        <x:v>32631317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10227,7 +10227,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26716280</x:v>
+        <x:v>28909083</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10319,7 +10319,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23077895</x:v>
+        <x:v>25109338</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10411,7 +10411,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6501383</x:v>
+        <x:v>18306607</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10503,7 +10503,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30951913</x:v>
+        <x:v>33106412</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10595,7 +10595,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27580951</x:v>
+        <x:v>25366032</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10687,7 +10687,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26340228</x:v>
+        <x:v>28232182</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10765,7 +10765,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22037519</x:v>
+        <x:v>24145158</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10809,14 +10809,14 @@
         <x:v>121</x:v>
       </x:c>
       <x:c>
-        <x:v>7120.85</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>7120.85</x:v>
+        <x:v>7228.54</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>7228.54</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -10843,7 +10843,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19568721</x:v>
+        <x:v>22452674</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10887,14 +10887,14 @@
         <x:v>18</x:v>
       </x:c>
       <x:c>
-        <x:v>1070.64</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>1070.64</x:v>
+        <x:v>1080.18</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>1080.18</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -10921,7 +10921,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31267851</x:v>
+        <x:v>23152131</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10965,14 +10965,14 @@
         <x:v>132</x:v>
       </x:c>
       <x:c>
-        <x:v>6679.2</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>6679.2</x:v>
+        <x:v>6618.48</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>6618.48</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -10999,7 +10999,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26046928</x:v>
+        <x:v>22657614</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11043,14 +11043,14 @@
         <x:v>456</x:v>
       </x:c>
       <x:c>
-        <x:v>14281.92</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>14281.92</x:v>
+        <x:v>14190.72</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>14190.72</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11077,7 +11077,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20244623</x:v>
+        <x:v>27692169</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11121,14 +11121,14 @@
         <x:v>135</x:v>
       </x:c>
       <x:c>
-        <x:v>6642</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>6642</x:v>
+        <x:v>6605.55</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>6605.55</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11155,7 +11155,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26850854</x:v>
+        <x:v>24643844</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11233,7 +11233,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29671317</x:v>
+        <x:v>31727002</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11277,14 +11277,14 @@
         <x:v>1178</x:v>
       </x:c>
       <x:c>
-        <x:v>18836.22</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>18836.22</x:v>
+        <x:v>18506.38</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>18506.38</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11311,7 +11311,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21190610</x:v>
+        <x:v>24380330</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11355,14 +11355,14 @@
         <x:v>337</x:v>
       </x:c>
       <x:c>
-        <x:v>18083.42</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>18083.42</x:v>
+        <x:v>17783.49</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>17783.49</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11389,7 +11389,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19991542</x:v>
+        <x:v>29090530</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11433,14 +11433,14 @@
         <x:v>122</x:v>
       </x:c>
       <x:c>
-        <x:v>53978.9</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>53978.9</x:v>
+        <x:v>53720.26</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>53720.26</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11467,7 +11467,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28250130</x:v>
+        <x:v>32116669</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11511,14 +11511,14 @@
         <x:v>390</x:v>
       </x:c>
       <x:c>
-        <x:v>36231</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>36231</x:v>
+        <x:v>36270</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>36270</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11545,7 +11545,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32985797</x:v>
+        <x:v>26152973</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11589,14 +11589,14 @@
         <x:v>170</x:v>
       </x:c>
       <x:c>
-        <x:v>6239</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>6239</x:v>
+        <x:v>6167.6</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>6167.6</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11623,7 +11623,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29022665</x:v>
+        <x:v>24252963</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11667,14 +11667,14 @@
         <x:v>2754</x:v>
       </x:c>
       <x:c>
-        <x:v>58880.52</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>58880.52</x:v>
+        <x:v>58219.56</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>58219.56</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11701,7 +11701,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31432903</x:v>
+        <x:v>31268538</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11745,14 +11745,14 @@
         <x:v>4582</x:v>
       </x:c>
       <x:c>
-        <x:v>42704.24</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>42704.24</x:v>
+        <x:v>42154.4</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>42154.4</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11779,7 +11779,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24849516</x:v>
+        <x:v>30878555</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11823,14 +11823,14 @@
         <x:v>230</x:v>
       </x:c>
       <x:c>
-        <x:v>7484.2</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>7484.2</x:v>
+        <x:v>7426.7</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>7426.7</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11857,7 +11857,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29148243</x:v>
+        <x:v>26726595</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11901,14 +11901,14 @@
         <x:v>290</x:v>
       </x:c>
       <x:c>
-        <x:v>19476.4</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>19476.4</x:v>
+        <x:v>19241.5</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>19241.5</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -11935,7 +11935,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31635542</x:v>
+        <x:v>28519751</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11979,14 +11979,14 @@
         <x:v>550</x:v>
       </x:c>
       <x:c>
-        <x:v>40755</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>40755</x:v>
+        <x:v>40304</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>40304</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -12013,7 +12013,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25613622</x:v>
+        <x:v>29295369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12057,14 +12057,14 @@
         <x:v>420</x:v>
       </x:c>
       <x:c>
-        <x:v>40110</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>40110</x:v>
+        <x:v>39811.8</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>39811.8</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -12091,7 +12091,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25771379</x:v>
+        <x:v>32917098</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12135,14 +12135,14 @@
         <x:v>81</x:v>
       </x:c>
       <x:c>
-        <x:v>6820.2</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>6820.2</x:v>
+        <x:v>6766.74</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>6766.74</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -12169,7 +12169,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31895692</x:v>
+        <x:v>12587185</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12213,14 +12213,14 @@
         <x:v>48</x:v>
       </x:c>
       <x:c>
-        <x:v>7504.32</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>7504.32</x:v>
+        <x:v>7471.68</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>7471.68</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -12247,7 +12247,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32937343</x:v>
+        <x:v>33446050</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12291,14 +12291,14 @@
         <x:v>61</x:v>
       </x:c>
       <x:c>
-        <x:v>7570.1</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>7570.1</x:v>
+        <x:v>7612.19</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>7612.19</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -12325,7 +12325,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27164209</x:v>
+        <x:v>20950212</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12369,14 +12369,14 @@
         <x:v>548</x:v>
       </x:c>
       <x:c>
-        <x:v>50744.8</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>50744.8</x:v>
+        <x:v>50925.64</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>50925.64</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -12403,7 +12403,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20515555</x:v>
+        <x:v>29998689</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12447,14 +12447,14 @@
         <x:v>435</x:v>
       </x:c>
       <x:c>
-        <x:v>35670</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>35670</x:v>
+        <x:v>35665.65</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>35665.65</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -12481,7 +12481,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20108385</x:v>
+        <x:v>33148419</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12525,14 +12525,14 @@
         <x:v>399</x:v>
       </x:c>
       <x:c>
-        <x:v>39892.02</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>39892.02</x:v>
+        <x:v>39824.19</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>39824.19</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -12559,7 +12559,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33283836</x:v>
+        <x:v>32798815</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12603,14 +12603,14 @@
         <x:v>306</x:v>
       </x:c>
       <x:c>
-        <x:v>36208.98</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>36208.98</x:v>
+        <x:v>36022.32</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>36022.32</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -12637,7 +12637,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25119128</x:v>
+        <x:v>24559935</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12681,14 +12681,14 @@
         <x:v>80</x:v>
       </x:c>
       <x:c>
-        <x:v>7255.2</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>7255.2</x:v>
+        <x:v>7245.6</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>7245.6</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -12715,7 +12715,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25206871</x:v>
+        <x:v>11088292</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12759,14 +12759,14 @@
         <x:v>52</x:v>
       </x:c>
       <x:c>
-        <x:v>8538.4</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>8538.4</x:v>
+        <x:v>8542.56</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>8542.56</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -12793,7 +12793,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30535474</x:v>
+        <x:v>23186118</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12837,14 +12837,14 @@
         <x:v>857</x:v>
       </x:c>
       <x:c>
-        <x:v>7790.13</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>7790.13</x:v>
+        <x:v>7798.7</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>7798.7</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -12871,7 +12871,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26053647</x:v>
+        <x:v>22455796</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12915,14 +12915,14 @@
         <x:v>94</x:v>
       </x:c>
       <x:c>
-        <x:v>7195.7</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>7195.7</x:v>
+        <x:v>7181.6</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>7181.6</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -12949,7 +12949,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10229151</x:v>
+        <x:v>31198230</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13019,7 +13019,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12250627</x:v>
+        <x:v>20392069</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13089,7 +13089,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31671938</x:v>
+        <x:v>33449910</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13159,7 +13159,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28114241</x:v>
+        <x:v>25895649</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13229,7 +13229,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7651483</x:v>
+        <x:v>20029112</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13299,7 +13299,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28102145</x:v>
+        <x:v>25985827</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13369,7 +13369,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28825240</x:v>
+        <x:v>26769484</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13439,7 +13439,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31750196</x:v>
+        <x:v>29673374</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13509,7 +13509,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23912046</x:v>
+        <x:v>21783829</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13579,7 +13579,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10594567</x:v>
+        <x:v>20154438</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13649,7 +13649,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32148406</x:v>
+        <x:v>29840531</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13719,7 +13719,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30375058</x:v>
+        <x:v>32140504</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13789,7 +13789,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24325144</x:v>
+        <x:v>21892533</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13859,7 +13859,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6775324</x:v>
+        <x:v>18354581</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13929,7 +13929,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8285114</x:v>
+        <x:v>19978795</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13997,7 +13997,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9649331</x:v>
+        <x:v>11238315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14041,16 +14041,16 @@
         <x:v>45.0186793</x:v>
       </x:c>
       <x:c>
-        <x:v>14754.95</x:v>
-      </x:c>
-      <x:c>
-        <x:v>57.36</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>14697.59</x:v>
+        <x:v>14761.43</x:v>
+      </x:c>
+      <x:c>
+        <x:v>58.82</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>14702.61</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -14077,7 +14077,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2405363</x:v>
+        <x:v>3318118</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14157,7 +14157,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17229067</x:v>
+        <x:v>14051130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14237,7 +14237,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11790050</x:v>
+        <x:v>13503025</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14317,7 +14317,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13808171</x:v>
+        <x:v>10223328</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14409,7 +14409,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7114037</x:v>
+        <x:v>4033448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14501,7 +14501,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12205561</x:v>
+        <x:v>8199289</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14593,7 +14593,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7246561</x:v>
+        <x:v>3745722</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14685,7 +14685,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10913461</x:v>
+        <x:v>12808258</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14763,7 +14763,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3670826</x:v>
+        <x:v>632881</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14841,7 +14841,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14090996</x:v>
+        <x:v>10475630</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14919,7 +14919,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6456992</x:v>
+        <x:v>7449017</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14997,7 +14997,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6551604</x:v>
+        <x:v>7373977</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15075,7 +15075,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12631086</x:v>
+        <x:v>8486909</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15153,7 +15153,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16373512</x:v>
+        <x:v>17827530</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15231,7 +15231,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>925047</x:v>
+        <x:v>2002016</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15309,7 +15309,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7023899</x:v>
+        <x:v>8033919</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15387,7 +15387,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11853455</x:v>
+        <x:v>13432035</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15465,7 +15465,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15953661</x:v>
+        <x:v>17700678</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15543,7 +15543,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1453081</x:v>
+        <x:v>2517238</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15621,7 +15621,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17455745</x:v>
+        <x:v>13946934</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15699,7 +15699,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13182952</x:v>
+        <x:v>9506119</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15777,7 +15777,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17681873</x:v>
+        <x:v>14318161</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15855,7 +15855,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7816220</x:v>
+        <x:v>4562384</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15933,7 +15933,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1467997</x:v>
+        <x:v>2498718</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16011,7 +16011,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5056302</x:v>
+        <x:v>6106480</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16089,7 +16089,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6496705</x:v>
+        <x:v>7354483</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16159,7 +16159,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3399178</x:v>
+        <x:v>492802</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16229,7 +16229,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16914783</x:v>
+        <x:v>13821224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16299,7 +16299,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11394505</x:v>
+        <x:v>12872571</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16369,7 +16369,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7741748</x:v>
+        <x:v>4625006</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16439,7 +16439,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15654480</x:v>
+        <x:v>17220743</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16509,7 +16509,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9817229</x:v>
+        <x:v>11535262</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16579,7 +16579,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2691438</x:v>
+        <x:v>3500636</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16649,7 +16649,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12025340</x:v>
+        <x:v>8451386</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16719,7 +16719,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10716823</x:v>
+        <x:v>12165761</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16789,7 +16789,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3481740</x:v>
+        <x:v>391912</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16857,7 +16857,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32784697</x:v>
+        <x:v>30685370</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -16937,7 +16937,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25514737</x:v>
+        <x:v>27918877</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17005,7 +17005,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31699723</x:v>
+        <x:v>33777411</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17085,7 +17085,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20476732</x:v>
+        <x:v>11142628</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17129,16 +17129,16 @@
         <x:v>27715.617034</x:v>
       </x:c>
       <x:c>
-        <x:v>153215.51</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1764.88</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>151450.63</x:v>
+        <x:v>153293.12</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1778.46</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>151514.66</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -17165,7 +17165,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25945392</x:v>
+        <x:v>28087202</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17209,16 +17209,16 @@
         <x:v>46778.6843965148</x:v>
       </x:c>
       <x:c>
-        <x:v>78717.54</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>78717.54</x:v>
+        <x:v>78809.16</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>78809.16</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -17245,7 +17245,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30660784</x:v>
+        <x:v>32806424</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17289,16 +17289,16 @@
         <x:v>59.67945939</x:v>
       </x:c>
       <x:c>
-        <x:v>31463.61</x:v>
-      </x:c>
-      <x:c>
-        <x:v>463.8</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>30999.81</x:v>
+        <x:v>31307.6</x:v>
+      </x:c>
+      <x:c>
+        <x:v>436.5</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>30871.1</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -17325,7 +17325,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19298638</x:v>
+        <x:v>732942</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17405,7 +17405,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24021929</x:v>
+        <x:v>21979940</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17485,7 +17485,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19210452</x:v>
+        <x:v>1393116</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17565,7 +17565,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33424197</x:v>
+        <x:v>31613879</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17609,16 +17609,16 @@
         <x:v>33808.77064958</x:v>
       </x:c>
       <x:c>
-        <x:v>35885.22</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>35885.22</x:v>
+        <x:v>35869.13</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>35869.13</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -17645,7 +17645,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32170428</x:v>
+        <x:v>30230361</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17729,7 +17729,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>33091939</x:v>
+        <x:v>31414892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17777,12 +17777,12 @@
         <x:v>24493.92532282</x:v>
       </x:c>
       <x:c>
-        <x:v>31031.18</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c>
-        <x:v>31031.18</x:v>
+        <x:v>31050.52</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c>
+        <x:v>31050.52</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -17813,7 +17813,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>21195502</x:v>
+        <x:v>31089823</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17905,7 +17905,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29031921</x:v>
+        <x:v>27080786</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -17997,7 +17997,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23896796</x:v>
+        <x:v>22018609</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18089,7 +18089,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33006723</x:v>
+        <x:v>31030126</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18126,7 +18126,7 @@
       <x:c/>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>MARFRIG</x:t>
+          <x:t>Marfrig</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -18181,7 +18181,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28760785</x:v>
+        <x:v>26816277</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18273,7 +18273,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24025693</x:v>
+        <x:v>21983330</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18365,7 +18365,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24687338</x:v>
+        <x:v>22792370</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18457,7 +18457,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20593888</x:v>
+        <x:v>10997501</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18549,7 +18549,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27137890</x:v>
+        <x:v>29423978</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18641,7 +18641,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23382208</x:v>
+        <x:v>21497383</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18733,7 +18733,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21816220</x:v>
+        <x:v>24133429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18825,7 +18825,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20823093</x:v>
+        <x:v>11931194</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -18917,7 +18917,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30938918</x:v>
+        <x:v>33058973</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19009,7 +19009,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27078992</x:v>
+        <x:v>29496645</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19101,7 +19101,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22080742</x:v>
+        <x:v>24445668</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19193,7 +19193,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21280131</x:v>
+        <x:v>23599269</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19285,7 +19285,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32671681</x:v>
+        <x:v>30859626</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19377,7 +19377,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24015889</x:v>
+        <x:v>21974085</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19469,7 +19469,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32415378</x:v>
+        <x:v>30576119</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19561,7 +19561,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25512893</x:v>
+        <x:v>27917041</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19653,7 +19653,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25744739</x:v>
+        <x:v>28187248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19745,7 +19745,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24797193</x:v>
+        <x:v>22736436</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19837,7 +19837,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22725404</x:v>
+        <x:v>24868004</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19929,7 +19929,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23096396</x:v>
+        <x:v>25625632</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20021,7 +20021,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23068134</x:v>
+        <x:v>25593930</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20113,7 +20113,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26796477</x:v>
+        <x:v>29313359</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20157,14 +20157,14 @@
         <x:v>600</x:v>
       </x:c>
       <x:c>
-        <x:v>11502</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>11502</x:v>
+        <x:v>11196</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>11196</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20191,7 +20191,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24928827</x:v>
+        <x:v>29192338</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20269,7 +20269,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5478137</x:v>
+        <x:v>19938421</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20313,14 +20313,14 @@
         <x:v>146</x:v>
       </x:c>
       <x:c>
-        <x:v>8592.1</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>8592.1</x:v>
+        <x:v>8724.96</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>8724.96</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20347,7 +20347,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22656827</x:v>
+        <x:v>32168775</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20391,14 +20391,14 @@
         <x:v>20</x:v>
       </x:c>
       <x:c>
-        <x:v>1189.6</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>1189.6</x:v>
+        <x:v>1200.4</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>1200.4</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20425,7 +20425,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33067647</x:v>
+        <x:v>32939781</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20469,14 +20469,14 @@
         <x:v>385</x:v>
       </x:c>
       <x:c>
-        <x:v>36740.55</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>36740.55</x:v>
+        <x:v>36755.95</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>36755.95</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20503,7 +20503,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13515161</x:v>
+        <x:v>28353475</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20547,14 +20547,14 @@
         <x:v>161</x:v>
       </x:c>
       <x:c>
-        <x:v>3664.36</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>3664.36</x:v>
+        <x:v>3546.83</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>3546.83</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20581,7 +20581,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24490602</x:v>
+        <x:v>22788213</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20625,14 +20625,14 @@
         <x:v>200</x:v>
       </x:c>
       <x:c>
-        <x:v>4850</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>4850</x:v>
+        <x:v>4806</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>4806</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20659,7 +20659,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33687711</x:v>
+        <x:v>28210369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20703,14 +20703,14 @@
         <x:v>190</x:v>
       </x:c>
       <x:c>
-        <x:v>17890.4</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>17890.4</x:v>
+        <x:v>17533.2</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>17533.2</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20737,7 +20737,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22865945</x:v>
+        <x:v>32392995</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20781,14 +20781,14 @@
         <x:v>56</x:v>
       </x:c>
       <x:c>
-        <x:v>4511.36</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>4511.36</x:v>
+        <x:v>4409.44</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>4409.44</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20815,7 +20815,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22604049</x:v>
+        <x:v>24328980</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20859,14 +20859,14 @@
         <x:v>1560</x:v>
       </x:c>
       <x:c>
-        <x:v>18564</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>18564</x:v>
+        <x:v>18501.6</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>18501.6</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20893,7 +20893,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27160574</x:v>
+        <x:v>30893296</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20937,14 +20937,14 @@
         <x:v>501</x:v>
       </x:c>
       <x:c>
-        <x:v>25350.6</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>25350.6</x:v>
+        <x:v>25180.26</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>25180.26</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -20971,7 +20971,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19243012</x:v>
+        <x:v>30948916</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21015,14 +21015,14 @@
         <x:v>1300</x:v>
       </x:c>
       <x:c>
-        <x:v>22763</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>22763</x:v>
+        <x:v>22529</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>22529</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -21049,7 +21049,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19388287</x:v>
+        <x:v>29599195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21093,14 +21093,14 @@
         <x:v>263</x:v>
       </x:c>
       <x:c>
-        <x:v>8237.16</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>8237.16</x:v>
+        <x:v>8184.56</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>8184.56</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -21127,7 +21127,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32487054</x:v>
+        <x:v>25459583</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21171,14 +21171,14 @@
         <x:v>231</x:v>
       </x:c>
       <x:c>
-        <x:v>11365.2</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>11365.2</x:v>
+        <x:v>11309.76</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>11309.76</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -21205,7 +21205,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28584991</x:v>
+        <x:v>29062309</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21249,14 +21249,14 @@
         <x:v>1320</x:v>
       </x:c>
       <x:c>
-        <x:v>34293.6</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>34293.6</x:v>
+        <x:v>33963.6</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>33963.6</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -21283,7 +21283,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>100196</x:v>
+        <x:v>24635903</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21361,7 +21361,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22281223</x:v>
+        <x:v>24799604</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21405,14 +21405,14 @@
         <x:v>1252</x:v>
       </x:c>
       <x:c>
-        <x:v>20019.48</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>20019.48</x:v>
+        <x:v>19706.48</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>19706.48</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -21439,7 +21439,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9011072</x:v>
+        <x:v>23925671</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21483,14 +21483,14 @@
         <x:v>262</x:v>
       </x:c>
       <x:c>
-        <x:v>14058.92</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>14058.92</x:v>
+        <x:v>13859.8</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>13859.8</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -21517,7 +21517,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19753969</x:v>
+        <x:v>24340244</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21561,14 +21561,14 @@
         <x:v>217</x:v>
       </x:c>
       <x:c>
-        <x:v>96011.65</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>96011.65</x:v>
+        <x:v>95447.45</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>95447.45</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -21595,7 +21595,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26223461</x:v>
+        <x:v>26858193</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21639,14 +21639,14 @@
         <x:v>367</x:v>
       </x:c>
       <x:c>
-        <x:v>34094.3</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>34094.3</x:v>
+        <x:v>34131</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>34131</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -21673,7 +21673,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20273783</x:v>
+        <x:v>22172865</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21717,14 +21717,14 @@
         <x:v>236</x:v>
       </x:c>
       <x:c>
-        <x:v>8661.2</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>8661.2</x:v>
+        <x:v>8569.16</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>8569.16</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -21751,7 +21751,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1570899</x:v>
+        <x:v>6166405</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21795,14 +21795,14 @@
         <x:v>3696</x:v>
       </x:c>
       <x:c>
-        <x:v>79020.48</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>79020.48</x:v>
+        <x:v>78059.52</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>78059.52</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -21829,7 +21829,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24012042</x:v>
+        <x:v>24797215</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21873,14 +21873,14 @@
         <x:v>45</x:v>
       </x:c>
       <x:c>
-        <x:v>2374.2</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>2374.2</x:v>
+        <x:v>2377.35</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>2377.35</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -21907,7 +21907,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23680904</x:v>
+        <x:v>17393375</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -21951,14 +21951,14 @@
         <x:v>965</x:v>
       </x:c>
       <x:c>
-        <x:v>8993.8</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>8993.8</x:v>
+        <x:v>8849.05</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>8849.05</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -21985,7 +21985,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23464156</x:v>
+        <x:v>24196150</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22029,14 +22029,14 @@
         <x:v>786</x:v>
       </x:c>
       <x:c>
-        <x:v>25576.44</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>25576.44</x:v>
+        <x:v>25395.66</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>25395.66</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -22063,7 +22063,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20417994</x:v>
+        <x:v>31069825</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22107,14 +22107,14 @@
         <x:v>600</x:v>
       </x:c>
       <x:c>
-        <x:v>27510</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>27510</x:v>
+        <x:v>27312</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>27312</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -22141,7 +22141,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23625390</x:v>
+        <x:v>23336292</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22185,14 +22185,14 @@
         <x:v>440</x:v>
       </x:c>
       <x:c>
-        <x:v>26914.8</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>26914.8</x:v>
+        <x:v>26589.2</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>26589.2</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -22219,7 +22219,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21655916</x:v>
+        <x:v>11901619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22263,14 +22263,14 @@
         <x:v>426</x:v>
       </x:c>
       <x:c>
-        <x:v>28610.16</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>28610.16</x:v>
+        <x:v>28260.84</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>28260.84</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -22297,7 +22297,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22224857</x:v>
+        <x:v>22353510</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22341,14 +22341,14 @@
         <x:v>33</x:v>
       </x:c>
       <x:c>
-        <x:v>1676.73</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>1676.73</x:v>
+        <x:v>1677.39</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>1677.39</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -22375,7 +22375,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28254946</x:v>
+        <x:v>24012993</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22419,14 +22419,14 @@
         <x:v>348</x:v>
       </x:c>
       <x:c>
-        <x:v>25786.8</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>25786.8</x:v>
+        <x:v>25497.96</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>25497.96</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -22453,7 +22453,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33844020</x:v>
+        <x:v>26148610</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22497,14 +22497,14 @@
         <x:v>612</x:v>
       </x:c>
       <x:c>
-        <x:v>58446</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>58446</x:v>
+        <x:v>58023.72</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>58023.72</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -22531,7 +22531,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31801289</x:v>
+        <x:v>28250922</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22575,14 +22575,14 @@
         <x:v>93</x:v>
       </x:c>
       <x:c>
-        <x:v>7830.6</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>7830.6</x:v>
+        <x:v>7775.73</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>7775.73</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -22609,7 +22609,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28586853</x:v>
+        <x:v>24093965</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22653,14 +22653,14 @@
         <x:v>55</x:v>
       </x:c>
       <x:c>
-        <x:v>8598.7</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>8598.7</x:v>
+        <x:v>8562.95</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>8562.95</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -22687,7 +22687,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32194551</x:v>
+        <x:v>22618191</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22731,14 +22731,14 @@
         <x:v>73</x:v>
       </x:c>
       <x:c>
-        <x:v>9059.3</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>9059.3</x:v>
+        <x:v>9115.51</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>9115.51</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -22765,7 +22765,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24547932</x:v>
+        <x:v>33498531</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22809,14 +22809,14 @@
         <x:v>288</x:v>
       </x:c>
       <x:c>
-        <x:v>26668.8</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>26668.8</x:v>
+        <x:v>26714.88</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>26714.88</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -22843,7 +22843,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23067794</x:v>
+        <x:v>25226554</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22887,14 +22887,14 @@
         <x:v>379</x:v>
       </x:c>
       <x:c>
-        <x:v>34864.21</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>34864.21</x:v>
+        <x:v>34723.98</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>34723.98</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -22921,7 +22921,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9241400</x:v>
+        <x:v>29653712</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -22965,14 +22965,14 @@
         <x:v>91</x:v>
       </x:c>
       <x:c>
-        <x:v>7462</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>7462</x:v>
+        <x:v>7461.09</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>7461.09</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -22999,7 +22999,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30962706</x:v>
+        <x:v>9776947</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23043,14 +23043,14 @@
         <x:v>284</x:v>
       </x:c>
       <x:c>
-        <x:v>28394.32</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>28394.32</x:v>
+        <x:v>28368.76</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>28368.76</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -23077,7 +23077,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29813359</x:v>
+        <x:v>26577859</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23121,14 +23121,14 @@
         <x:v>229</x:v>
       </x:c>
       <x:c>
-        <x:v>27097.57</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>27097.57</x:v>
+        <x:v>26960.17</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>26960.17</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -23155,7 +23155,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17847581</x:v>
+        <x:v>26721898</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23199,14 +23199,14 @@
         <x:v>100</x:v>
       </x:c>
       <x:c>
-        <x:v>9069</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>9069</x:v>
+        <x:v>9070</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>9070</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -23233,7 +23233,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28584349</x:v>
+        <x:v>22457595</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23277,14 +23277,14 @@
         <x:v>62</x:v>
       </x:c>
       <x:c>
-        <x:v>10180.4</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>10180.4</x:v>
+        <x:v>10182.88</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>10182.88</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -23311,7 +23311,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21826053</x:v>
+        <x:v>26094974</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23389,7 +23389,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>20240563</x:v>
+        <x:v>9310447</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23433,14 +23433,14 @@
         <x:v>107</x:v>
       </x:c>
       <x:c>
-        <x:v>8190.85</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>8190.85</x:v>
+        <x:v>8173.73</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>8173.73</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -23467,7 +23467,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25513452</x:v>
+        <x:v>20286702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23537,7 +23537,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21643237</x:v>
+        <x:v>23848741</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23607,7 +23607,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23154458</x:v>
+        <x:v>25580563</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23677,7 +23677,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>26766347</x:v>
+        <x:v>29316691</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23747,7 +23747,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31932945</x:v>
+        <x:v>29994982</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23817,7 +23817,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24522654</x:v>
+        <x:v>22473777</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23887,7 +23887,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33195064</x:v>
+        <x:v>31385606</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23957,7 +23957,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>31948672</x:v>
+        <x:v>29977631</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24027,7 +24027,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22687281</x:v>
+        <x:v>24966741</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24097,7 +24097,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5515156</x:v>
+        <x:v>19839196</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24167,7 +24167,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5073795</x:v>
+        <x:v>19931842</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24237,7 +24237,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32590942</x:v>
+        <x:v>30877013</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24307,7 +24307,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29187703</x:v>
+        <x:v>27375363</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24377,7 +24377,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>130972</x:v>
+        <x:v>17359071</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24447,7 +24447,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22649344</x:v>
+        <x:v>25027750</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24517,7 +24517,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25292712</x:v>
+        <x:v>23264446</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24587,7 +24587,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25160176</x:v>
+        <x:v>23395755</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24657,7 +24657,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29272496</x:v>
+        <x:v>27296773</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24727,7 +24727,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33400612</x:v>
+        <x:v>31719872</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24797,7 +24797,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21592604</x:v>
+        <x:v>23902057</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24867,7 +24867,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19730525</x:v>
+        <x:v>6346946</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24937,7 +24937,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30370392</x:v>
+        <x:v>32615110</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25007,7 +25007,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32268395</x:v>
+        <x:v>30193084</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25077,7 +25077,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21437043</x:v>
+        <x:v>23493650</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25147,7 +25147,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19594869</x:v>
+        <x:v>1643463</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25217,7 +25217,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19223931</x:v>
+        <x:v>1414929</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25285,7 +25285,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1980813</x:v>
+        <x:v>5897085</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25365,7 +25365,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>506325</x:v>
+        <x:v>4642773</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25457,7 +25457,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10912391</x:v>
+        <x:v>15430698</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25549,7 +25549,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8878635</x:v>
+        <x:v>8219014</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25641,7 +25641,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6840185</x:v>
+        <x:v>10692739</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25733,7 +25733,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15938938</x:v>
+        <x:v>19072567</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25825,7 +25825,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14537836</x:v>
+        <x:v>13781177</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -25917,7 +25917,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11639261</x:v>
+        <x:v>15762651</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26009,7 +26009,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14704903</x:v>
+        <x:v>18608098</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26101,7 +26101,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8355296</x:v>
+        <x:v>7645136</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26193,7 +26193,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1446417</x:v>
+        <x:v>5313535</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26285,7 +26285,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6264031</x:v>
+        <x:v>10110946</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26377,7 +26377,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13435626</x:v>
+        <x:v>12915176</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26455,7 +26455,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16299642</x:v>
+        <x:v>19461757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26523,7 +26523,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22926981</x:v>
+        <x:v>25219048</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26607,7 +26607,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>29524132</x:v>
+        <x:v>27584312</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26675,7 +26675,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>23721825</x:v>
+        <x:v>21683667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26759,7 +26759,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>27633778</x:v>
+        <x:v>25847311</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26827,7 +26827,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25908331</x:v>
+        <x:v>28052045</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26871,16 +26871,16 @@
         <x:v>0.4881686</x:v>
       </x:c>
       <x:c>
-        <x:v>437.04</x:v>
-      </x:c>
-      <x:c>
-        <x:v>3.22</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>433.82</x:v>
+        <x:v>437.25</x:v>
+      </x:c>
+      <x:c>
+        <x:v>3.25</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>434</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -26907,7 +26907,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12396170</x:v>
+        <x:v>17295339</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26987,7 +26987,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4611762</x:v>
+        <x:v>19923406</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27067,7 +27067,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22859811</x:v>
+        <x:v>25283171</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27147,7 +27147,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24905565</x:v>
+        <x:v>23104322</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27191,16 +27191,16 @@
         <x:v>8017.62959</x:v>
       </x:c>
       <x:c>
-        <x:v>28243.46</x:v>
-      </x:c>
-      <x:c>
-        <x:v>230.43</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>28013.03</x:v>
+        <x:v>28257.77</x:v>
+      </x:c>
+      <x:c>
+        <x:v>232.65</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>28025.12</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -27227,7 +27227,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>45687</x:v>
+        <x:v>17372254</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27295,7 +27295,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30680826</x:v>
+        <x:v>32792281</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27339,16 +27339,16 @@
         <x:v>1679.54166587</x:v>
       </x:c>
       <x:c>
-        <x:v>9393.03</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>9393.03</x:v>
+        <x:v>9519.39</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>9519.39</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -27375,7 +27375,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10679571</x:v>
+        <x:v>20266176</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27455,7 +27455,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21847636</x:v>
+        <x:v>24198502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27533,7 +27533,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14634861</x:v>
+        <x:v>20813617</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27603,7 +27603,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>29194295</x:v>
+        <x:v>27381401</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27671,7 +27671,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17981636</x:v>
+        <x:v>14579205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27751,7 +27751,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15062971</x:v>
+        <x:v>16197248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27843,7 +27843,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>14120428</x:v>
+        <x:v>10373608</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -27935,7 +27935,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4094097</x:v>
+        <x:v>668695</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28003,7 +28003,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>28467498</x:v>
+        <x:v>26111130</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28071,7 +28071,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32649918</x:v>
+        <x:v>30330946</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28139,7 +28139,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11489440</x:v>
+        <x:v>13342417</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28187,12 +28187,12 @@
         <x:v>434890.82128813</x:v>
       </x:c>
       <x:c>
-        <x:v>550960.14</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c>
-        <x:v>550960.14</x:v>
+        <x:v>551303.44</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c>
+        <x:v>551303.44</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -28223,7 +28223,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>6787701</x:v>
+        <x:v>6039807</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28271,12 +28271,12 @@
         <x:v>117927.16105932</x:v>
       </x:c>
       <x:c>
-        <x:v>149401.09</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c>
-        <x:v>149401.09</x:v>
+        <x:v>149494.19</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c>
+        <x:v>149494.19</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -28307,7 +28307,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>2012875</x:v>
+        <x:v>2576813</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28355,12 +28355,12 @@
         <x:v>205429.02166211</x:v>
       </x:c>
       <x:c>
-        <x:v>336478.75</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c>
-        <x:v>336478.75</x:v>
+        <x:v>336624.58</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c>
+        <x:v>336624.58</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -28391,7 +28391,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>17104196</x:v>
+        <x:v>5777476</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28439,12 +28439,12 @@
         <x:v>137454.57196021</x:v>
       </x:c>
       <x:c>
-        <x:v>203552.85</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c>
-        <x:v>203552.85</x:v>
+        <x:v>204467.68</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c>
+        <x:v>204467.68</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -28475,7 +28475,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>609733</x:v>
+        <x:v>5564295</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28523,12 +28523,12 @@
         <x:v>228072.49772746</x:v>
       </x:c>
       <x:c>
-        <x:v>315964.65</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c>
-        <x:v>315964.65</x:v>
+        <x:v>316158.99</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c>
+        <x:v>316158.99</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -28559,7 +28559,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>2085118</x:v>
+        <x:v>6789833</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28651,7 +28651,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5988321</x:v>
+        <x:v>6953979</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28743,7 +28743,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3983805</x:v>
+        <x:v>736769</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28835,7 +28835,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2099058</x:v>
+        <x:v>3009679</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28927,7 +28927,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11799307</x:v>
+        <x:v>13545813</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29019,7 +29019,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1759633</x:v>
+        <x:v>2807329</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29111,7 +29111,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3854786</x:v>
+        <x:v>521834</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29203,7 +29203,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4708381</x:v>
+        <x:v>1290053</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29295,7 +29295,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6485389</x:v>
+        <x:v>7441789</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29387,7 +29387,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11857429</x:v>
+        <x:v>13436234</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29479,7 +29479,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11597211</x:v>
+        <x:v>13215456</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29571,7 +29571,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11363958</x:v>
+        <x:v>12840140</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29663,7 +29663,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16546219</x:v>
+        <x:v>18172410</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29755,7 +29755,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>15944459</x:v>
+        <x:v>17044257</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29847,7 +29847,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>4717085</x:v>
+        <x:v>1272383</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29939,7 +29939,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6870560</x:v>
+        <x:v>8184091</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30031,7 +30031,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7903263</x:v>
+        <x:v>4387203</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30123,7 +30123,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16389490</x:v>
+        <x:v>17880807</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30215,7 +30215,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5004220</x:v>
+        <x:v>6188768</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30307,7 +30307,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>13203541</x:v>
+        <x:v>9557625</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30399,7 +30399,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12159343</x:v>
+        <x:v>8318813</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30491,7 +30491,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16271348</x:v>
+        <x:v>17993930</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30583,7 +30583,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11615263</x:v>
+        <x:v>13202232</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30675,7 +30675,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6550380</x:v>
+        <x:v>7373150</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30767,7 +30767,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10296602</x:v>
+        <x:v>11679043</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30859,7 +30859,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2619291</x:v>
+        <x:v>3563349</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30951,7 +30951,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6913083</x:v>
+        <x:v>8057450</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31043,7 +31043,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>5825096</x:v>
+        <x:v>6610300</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31111,7 +31111,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10292755</x:v>
+        <x:v>14741697</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31179,7 +31179,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17815693</x:v>
+        <x:v>17546984</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31223,16 +31223,16 @@
         <x:v>375.6534791</x:v>
       </x:c>
       <x:c>
-        <x:v>123121.1</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1279.9</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>121841.2</x:v>
+        <x:v>123175.13</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1290.87</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>121884.26</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -31259,7 +31259,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7171188</x:v>
+        <x:v>6547851</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31339,7 +31339,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>454089</x:v>
+        <x:v>4130974</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31419,7 +31419,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>648028</x:v>
+        <x:v>4413826</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31463,16 +31463,16 @@
         <x:v>39384.243258</x:v>
       </x:c>
       <x:c>
-        <x:v>79957.75</x:v>
-      </x:c>
-      <x:c>
-        <x:v>668.71</x:v>
-      </x:c>
-      <x:c>
-        <x:v>29.26</x:v>
-      </x:c>
-      <x:c>
-        <x:v>79259.78</x:v>
+        <x:v>79985.88</x:v>
+      </x:c>
+      <x:c>
+        <x:v>675.86</x:v>
+      </x:c>
+      <x:c>
+        <x:v>23.58</x:v>
+      </x:c>
+      <x:c>
+        <x:v>79286.44</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -31499,7 +31499,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2550917</x:v>
+        <x:v>1925775</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31579,7 +31579,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9899489</x:v>
+        <x:v>14445268</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31623,16 +31623,16 @@
         <x:v>1172.9169745</x:v>
       </x:c>
       <x:c>
-        <x:v>53409.92</x:v>
-      </x:c>
-      <x:c>
-        <x:v>552.56</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>52857.36</x:v>
+        <x:v>53443.31</x:v>
+      </x:c>
+      <x:c>
+        <x:v>559.24</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>52884.07</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -31659,7 +31659,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8009881</x:v>
+        <x:v>7338594</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31739,7 +31739,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>2855940</x:v>
+        <x:v>2248420</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31783,14 +31783,14 @@
         <x:v>2211</x:v>
       </x:c>
       <x:c>
-        <x:v>210995.73</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>210995.73</x:v>
+        <x:v>211084.17</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>211084.17</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -31817,7 +31817,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>8091180</x:v>
+        <x:v>18419121</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31861,14 +31861,14 @@
         <x:v>2126</x:v>
       </x:c>
       <x:c>
-        <x:v>197505.4</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>197505.4</x:v>
+        <x:v>197718</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>197718</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -31895,7 +31895,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>17200628</x:v>
+        <x:v>13538540</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31939,14 +31939,14 @@
         <x:v>2054</x:v>
       </x:c>
       <x:c>
-        <x:v>151996</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>151996</x:v>
+        <x:v>150517.12</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>150517.12</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -31973,7 +31973,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12155798</x:v>
+        <x:v>7033538</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32017,14 +32017,14 @@
         <x:v>2138</x:v>
       </x:c>
       <x:c>
-        <x:v>202767.92</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>202767.92</x:v>
+        <x:v>202661.02</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>202661.02</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -32051,7 +32051,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7920408</x:v>
+        <x:v>18107243</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32095,14 +32095,14 @@
         <x:v>1784</x:v>
       </x:c>
       <x:c>
-        <x:v>150230.64</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>150230.64</x:v>
+        <x:v>149124.56</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>149124.56</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -32129,7 +32129,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>9453040</x:v>
+        <x:v>3284221</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32173,14 +32173,14 @@
         <x:v>1592</x:v>
       </x:c>
       <x:c>
-        <x:v>147785.36</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>147785.36</x:v>
+        <x:v>147673.92</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>147673.92</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -32207,7 +32207,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3515630</x:v>
+        <x:v>10164552</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32251,14 +32251,14 @@
         <x:v>2156</x:v>
       </x:c>
       <x:c>
-        <x:v>198157.96</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>198157.96</x:v>
+        <x:v>197532.72</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>197532.72</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -32285,7 +32285,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6500117</x:v>
+        <x:v>6102778</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32329,14 +32329,14 @@
         <x:v>1753</x:v>
       </x:c>
       <x:c>
-        <x:v>143746</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>143746</x:v>
+        <x:v>143728.47</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>143728.47</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -32363,7 +32363,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>16602102</x:v>
+        <x:v>3591241</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32407,14 +32407,14 @@
         <x:v>1546</x:v>
       </x:c>
       <x:c>
-        <x:v>154569.08</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>154569.08</x:v>
+        <x:v>154445.4</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>154445.4</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -32441,7 +32441,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6546919</x:v>
+        <x:v>6131446</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32485,14 +32485,14 @@
         <x:v>1226</x:v>
       </x:c>
       <x:c>
-        <x:v>145072.58</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c/>
-      <x:c>
-        <x:v>145072.58</x:v>
+        <x:v>144410.54</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c/>
+      <x:c>
+        <x:v>144410.54</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -32519,7 +32519,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>3416690</x:v>
+        <x:v>18930470</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32589,7 +32589,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10913072</x:v>
+        <x:v>15430733</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32659,7 +32659,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18249783</x:v>
+        <x:v>17696227</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32729,7 +32729,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18393201</x:v>
+        <x:v>18068551</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32797,7 +32797,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>7482695</x:v>
+        <x:v>4265219</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32841,16 +32841,16 @@
         <x:v>63.6322495</x:v>
       </x:c>
       <x:c>
-        <x:v>36400.53</x:v>
-      </x:c>
-      <x:c>
-        <x:v>164.47</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>36236.06</x:v>
+        <x:v>36419</x:v>
+      </x:c>
+      <x:c>
+        <x:v>168.63</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>36250.37</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -32877,7 +32877,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6657775</x:v>
+        <x:v>7802726</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32957,7 +32957,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>12948509</x:v>
+        <x:v>8786605</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -33037,7 +33037,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>6118446</x:v>
+        <x:v>7319981</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -33081,16 +33081,16 @@
         <x:v>65284.49678</x:v>
       </x:c>
       <x:c>
-        <x:v>132540.36</x:v>
-      </x:c>
-      <x:c>
-        <x:v>571.58</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>131968.78</x:v>
+        <x:v>132586.98</x:v>
+      </x:c>
+      <x:c>
+        <x:v>582.07</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>132004.91</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -33117,7 +33117,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19140249</x:v>
+        <x:v>15684873</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -33197,7 +33197,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>18172862</x:v>
+        <x:v>14986913</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -33241,16 +33241,16 @@
         <x:v>16368.71616417</x:v>
       </x:c>
       <x:c>
-        <x:v>19775.48</x:v>
-      </x:c>
-      <x:c>
-        <x:v>235.95</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>19539.53</x:v>
+        <x:v>19785.42</x:v>
+      </x:c>
+      <x:c>
+        <x:v>238.19</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>19547.23</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -33277,7 +33277,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>1823195</x:v>
+        <x:v>2767009</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -33369,7 +33369,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11480504</x:v>
+        <x:v>13332956</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -33437,7 +33437,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>30949640</x:v>
+        <x:v>33106068</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -33517,7 +33517,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22440969</x:v>
+        <x:v>24686064</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -33585,7 +33585,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>25780096</x:v>
+        <x:v>27775167</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -33629,16 +33629,16 @@
         <x:v>718.2096246</x:v>
       </x:c>
       <x:c>
-        <x:v>235394.5</x:v>
-      </x:c>
-      <x:c>
-        <x:v>2859.18</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>232535.32</x:v>
+        <x:v>235497.78</x:v>
+      </x:c>
+      <x:c>
+        <x:v>2882.42</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>232615.36</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -33665,7 +33665,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>22056531</x:v>
+        <x:v>24130826</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -33709,16 +33709,16 @@
         <x:v>260006.11957</x:v>
       </x:c>
       <x:c>
-        <x:v>352897</x:v>
-      </x:c>
-      <x:c>
-        <x:v>4281.02</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>348615.98</x:v>
+        <x:v>353077.68</x:v>
+      </x:c>
+      <x:c>
+        <x:v>4321.67</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>348756.01</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -33745,7 +33745,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>24772362</x:v>
+        <x:v>22527988</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -33825,7 +33825,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>19920139</x:v>
+        <x:v>7511891</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -33869,16 +33869,16 @@
         <x:v>23314.3431286</x:v>
       </x:c>
       <x:c>
-        <x:v>128884.7</x:v>
-      </x:c>
-      <x:c>
-        <x:v>1510.19</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>127374.51</x:v>
+        <x:v>128949.99</x:v>
+      </x:c>
+      <x:c>
+        <x:v>1524.88</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>127425.11</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -33905,7 +33905,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33034427</x:v>
+        <x:v>30551765</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -33985,7 +33985,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>11509304</x:v>
+        <x:v>20459288</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -34065,7 +34065,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>32316655</x:v>
+        <x:v>30135092</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -34109,16 +34109,16 @@
         <x:v>105585.00641</x:v>
       </x:c>
       <x:c>
-        <x:v>235446.12</x:v>
-      </x:c>
-      <x:c>
-        <x:v>2866.09</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>232580.03</x:v>
+        <x:v>235578.38</x:v>
+      </x:c>
+      <x:c>
+        <x:v>2895.85</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>232682.53</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -34145,7 +34145,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>33183900</x:v>
+        <x:v>30873194</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -34189,16 +34189,16 @@
         <x:v>7718.50621968</x:v>
       </x:c>
       <x:c>
-        <x:v>351469.71</x:v>
-      </x:c>
-      <x:c>
-        <x:v>4011.43</x:v>
-      </x:c>
-      <x:c>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c>
-        <x:v>347458.28</x:v>
+        <x:v>351689.44</x:v>
+      </x:c>
+      <x:c>
+        <x:v>4060.86</x:v>
+      </x:c>
+      <x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c>
+        <x:v>347628.58</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -34225,7 +34225,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27196263</x:v>
+        <x:v>28948210</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -34305,7 +34305,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>27105341</x:v>
+        <x:v>29021426</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -34385,7 +34385,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>21831597</x:v>
+        <x:v>23788036</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -34477,7 +34477,7 @@
       </x:c>
       <x:c/>
       <x:c s="10">
-        <x:v>10201204</x:v>
+        <x:v>20192790</x:v>
       </x:c>
     </x:row>
     <x:row/>
